--- a/input/old/Metadata _POD Confirmation is missing for _ 30 days_TAD_10_01_DLV_POD.xlsx
+++ b/input/old/Metadata _POD Confirmation is missing for _ 30 days_TAD_10_01_DLV_POD.xlsx
@@ -422,7 +422,7 @@
         <v>Created on</v>
       </c>
       <c r="B6" t="str">
-        <v>14.01.2026 at 16:51 by ILIYAR</v>
+        <v>14.01.2026 at 16:51 by REDACTED</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +430,7 @@
         <v>Updated on</v>
       </c>
       <c r="B7" t="str">
-        <v>14.01.2026 at 16:55 by ILIYAR</v>
+        <v>14.01.2026 at 16:55 by REDACTED</v>
       </c>
     </row>
     <row r="8">
